--- a/examples/HFP_john+sally.xlsx
+++ b/examples/HFP_john+sally.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,60 +432,70 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>gross earnings</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>months worked</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -495,16 +505,31 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -512,16 +537,31 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -529,16 +569,31 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -546,16 +601,31 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -563,16 +633,31 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -589,13 +674,26 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>15000</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -603,16 +701,31 @@
       <c r="A8" t="n">
         <v>2027</v>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -620,16 +733,31 @@
       <c r="A9" t="n">
         <v>2028</v>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -637,16 +765,31 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -654,16 +797,31 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -671,16 +829,31 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -688,16 +861,31 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -705,16 +893,31 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -722,16 +925,31 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -739,16 +957,31 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -756,16 +989,31 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -773,16 +1021,31 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -790,16 +1053,31 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -807,16 +1085,31 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -824,16 +1117,31 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -841,16 +1149,31 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -858,16 +1181,31 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -875,16 +1213,31 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -892,16 +1245,31 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -909,16 +1277,31 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -926,16 +1309,31 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -943,16 +1341,31 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -960,16 +1373,31 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -977,16 +1405,31 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -994,16 +1437,31 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1011,16 +1469,31 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1028,16 +1501,31 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1045,16 +1533,31 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1062,16 +1565,31 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1079,16 +1597,31 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1096,16 +1629,31 @@
       <c r="A37" t="n">
         <v>2056</v>
       </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1120,7 +1668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,60 +1684,70 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>gross earnings</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>months worked</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Roth conv fixed</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -1199,16 +1757,31 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1216,16 +1789,31 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1233,16 +1821,31 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1250,16 +1853,31 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1267,16 +1885,31 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1284,16 +1917,31 @@
       <c r="A7" t="n">
         <v>2026</v>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1301,16 +1949,31 @@
       <c r="A8" t="n">
         <v>2027</v>
       </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1318,16 +1981,31 @@
       <c r="A9" t="n">
         <v>2028</v>
       </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1335,16 +2013,31 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1352,16 +2045,31 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1369,16 +2077,31 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1386,16 +2109,31 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1403,16 +2141,31 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1420,16 +2173,31 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1437,16 +2205,31 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1454,16 +2237,31 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1471,16 +2269,31 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1488,16 +2301,31 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1505,16 +2333,31 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1522,16 +2365,31 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1539,16 +2397,31 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1556,16 +2429,31 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1573,16 +2461,31 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1590,16 +2493,31 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1607,16 +2525,31 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1624,16 +2557,31 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1641,16 +2589,31 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1658,16 +2621,31 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1675,16 +2653,31 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1692,16 +2685,31 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1709,16 +2717,31 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1726,16 +2749,31 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1743,16 +2781,31 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1760,16 +2813,31 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1777,16 +2845,31 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1794,16 +2877,31 @@
       <c r="A37" t="n">
         <v>2056</v>
       </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1811,16 +2909,31 @@
       <c r="A38" t="n">
         <v>2057</v>
       </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1828,16 +2941,31 @@
       <c r="A39" t="n">
         <v>2058</v>
       </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1845,16 +2973,31 @@
       <c r="A40" t="n">
         <v>2059</v>
       </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1871,10 +3014,6 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/examples/HFP_john+sally.xlsx
+++ b/examples/HFP_john+sally.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,70 +432,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>gross earnings</t>
+          <t>other inc</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>months worked</t>
+          <t>net inv</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>other inc</t>
+          <t>taxable ctrb</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>net inv</t>
+          <t>401k ctrb</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>taxable ctrb</t>
+          <t>Roth 401k ctrb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>401k ctrb</t>
+          <t>IRA ctrb</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Roth 401k ctrb</t>
+          <t>Roth IRA ctrb</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>IRA ctrb</t>
+          <t>Roth conv</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Roth IRA ctrb</t>
+          <t>Roth conv fixed</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Roth conv</t>
+          <t>QCD</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Roth conv fixed</t>
+          <t>big-ticket items</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>QCD</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>big-ticket items</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -505,31 +495,16 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -537,31 +512,16 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -569,31 +529,16 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -601,31 +546,16 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -633,31 +563,16 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -674,26 +589,13 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
         <v>15000</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -701,31 +603,16 @@
       <c r="A8" t="n">
         <v>2027</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -733,31 +620,16 @@
       <c r="A9" t="n">
         <v>2028</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -765,31 +637,16 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -797,31 +654,16 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -829,31 +671,16 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -861,31 +688,16 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
       <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -893,31 +705,16 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
       <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -925,31 +722,16 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
       <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -957,31 +739,16 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
       <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -989,31 +756,16 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
       <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1021,31 +773,16 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1053,31 +790,16 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1085,31 +807,16 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1117,31 +824,16 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
       <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1149,31 +841,16 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
       <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1181,31 +858,16 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
       <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1213,31 +875,16 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
       <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1245,31 +892,16 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
       <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1277,31 +909,16 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
       <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1309,31 +926,16 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
       <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1341,31 +943,16 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
       <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1373,31 +960,16 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
       <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1405,31 +977,16 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
       <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1437,31 +994,16 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
       <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1469,31 +1011,16 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
       <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1501,31 +1028,16 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
       <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1533,31 +1045,16 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
       <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1565,31 +1062,16 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
       <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1597,31 +1079,16 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1629,31 +1096,16 @@
       <c r="A37" t="n">
         <v>2056</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
       <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1668,7 +1120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1684,70 +1136,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>gross earnings</t>
+          <t>other inc</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>months worked</t>
+          <t>net inv</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>other inc</t>
+          <t>taxable ctrb</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>net inv</t>
+          <t>401k ctrb</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>taxable ctrb</t>
+          <t>Roth 401k ctrb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>401k ctrb</t>
+          <t>IRA ctrb</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Roth 401k ctrb</t>
+          <t>Roth IRA ctrb</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>IRA ctrb</t>
+          <t>Roth conv</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Roth IRA ctrb</t>
+          <t>Roth conv fixed</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Roth conv</t>
+          <t>QCD</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Roth conv fixed</t>
+          <t>big-ticket items</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>QCD</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>big-ticket items</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -1757,31 +1199,16 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1789,31 +1216,16 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1821,31 +1233,16 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1853,31 +1250,16 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
       <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1885,31 +1267,16 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1917,31 +1284,16 @@
       <c r="A7" t="n">
         <v>2026</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
       <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1949,31 +1301,16 @@
       <c r="A8" t="n">
         <v>2027</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1981,31 +1318,16 @@
       <c r="A9" t="n">
         <v>2028</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2013,31 +1335,16 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
       <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2045,31 +1352,16 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
       <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2077,31 +1369,16 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2109,31 +1386,16 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
       <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2141,31 +1403,16 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
       <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2173,31 +1420,16 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
       <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2205,31 +1437,16 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
       <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2237,31 +1454,16 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
       <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2269,31 +1471,16 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2301,31 +1488,16 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2333,31 +1505,16 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2365,31 +1522,16 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
       <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2397,31 +1539,16 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
       <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2429,31 +1556,16 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
       <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2461,31 +1573,16 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
       <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2493,31 +1590,16 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
       <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2525,31 +1607,16 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
       <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2557,31 +1624,16 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
       <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2589,31 +1641,16 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
       <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2621,31 +1658,16 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
       <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2653,31 +1675,16 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
       <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2685,31 +1692,16 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
       <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2717,31 +1709,16 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
       <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2749,31 +1726,16 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
       <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2781,31 +1743,16 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
       <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2813,31 +1760,16 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
       <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2845,31 +1777,16 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2877,31 +1794,16 @@
       <c r="A37" t="n">
         <v>2056</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
       <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2909,31 +1811,16 @@
       <c r="A38" t="n">
         <v>2057</v>
       </c>
-      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
       <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2941,31 +1828,16 @@
       <c r="A39" t="n">
         <v>2058</v>
       </c>
-      <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
       <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2973,31 +1845,16 @@
       <c r="A40" t="n">
         <v>2059</v>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
       <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3014,6 +1871,10 @@
   </sheetPr>
   <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
